--- a/salidas/Cuadro_Terceros_DIAN_2026-09.xlsx
+++ b/salidas/Cuadro_Terceros_DIAN_2026-09.xlsx
@@ -2766,6 +2766,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H546"/>
